--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>45000</x:v>
+        <x:v>47246.35928</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.6</x:v>
+        <x:v>4.72208</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>1.5</x:v>
+        <x:v>0.9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>47246.35928</x:v>
+        <x:v>47320</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.72208</x:v>
+        <x:v>4.63</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">

--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>47320</x:v>
+        <x:v>47280</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.63</x:v>
+        <x:v>4.68</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">

--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -581,7 +581,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>47280</x:v>
+        <x:v>47320</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.68</x:v>
+        <x:v>4.65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">

--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -592,7 +592,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.65</x:v>
+        <x:v>4.7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -603,7 +603,7 @@
         <x:v>%</x:v>
       </x:c>
       <x:c r="C9" s="36">
-        <x:v>0.9</x:v>
+        <x:v>0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
